--- a/图片计算-实验参数表.xlsx
+++ b/图片计算-实验参数表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9555"/>
+    <workbookView windowWidth="24750" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="图片计算参数表" sheetId="1" r:id="rId1"/>
@@ -190,14 +190,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,148 +646,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1147,7 +1140,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
@@ -1177,16 +1170,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D2">
         <v>250</v>
       </c>
       <c r="E2">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F2">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1197,16 +1190,16 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D3">
         <v>250</v>
       </c>
       <c r="E3">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F3">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1217,16 +1210,16 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D4">
         <v>500</v>
       </c>
       <c r="E4">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F4">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1237,16 +1230,16 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D5">
         <v>500</v>
       </c>
       <c r="E5">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F5">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1257,16 +1250,16 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D6">
         <v>250</v>
       </c>
       <c r="E6">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F6">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1277,16 +1270,16 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D7">
         <v>250</v>
       </c>
       <c r="E7">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F7">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1297,16 +1290,16 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D8">
         <v>500</v>
       </c>
       <c r="E8">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F8">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1317,16 +1310,16 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D9">
         <v>500</v>
       </c>
       <c r="E9">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F9">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1337,16 +1330,16 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D10">
         <v>250</v>
       </c>
       <c r="E10">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F10">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1357,16 +1350,16 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D11">
         <v>250</v>
       </c>
       <c r="E11">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F11">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1377,16 +1370,16 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D12">
         <v>500</v>
       </c>
       <c r="E12">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F12">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1397,16 +1390,16 @@
         <v>7</v>
       </c>
       <c r="C13">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D13">
         <v>500</v>
       </c>
       <c r="E13">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F13">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1417,16 +1410,16 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D14">
         <v>250</v>
       </c>
       <c r="E14">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F14">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1437,16 +1430,16 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D15">
         <v>250</v>
       </c>
       <c r="E15">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F15">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1457,16 +1450,16 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D16">
         <v>500</v>
       </c>
       <c r="E16">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F16">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1477,16 +1470,16 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D17">
         <v>500</v>
       </c>
       <c r="E17">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F17">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1497,16 +1490,16 @@
         <v>24</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="D18">
         <v>375</v>
       </c>
       <c r="E18">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F18">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1517,16 +1510,16 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D19">
         <v>375</v>
       </c>
       <c r="E19">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F19">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1537,16 +1530,16 @@
         <v>24</v>
       </c>
       <c r="C20">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D20">
         <v>250</v>
       </c>
       <c r="E20">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F20">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1557,16 +1550,16 @@
         <v>24</v>
       </c>
       <c r="C21">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D21">
         <v>500</v>
       </c>
       <c r="E21">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F21">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1577,16 +1570,16 @@
         <v>24</v>
       </c>
       <c r="C22">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D22">
         <v>375</v>
       </c>
       <c r="E22">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="F22">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1597,16 +1590,16 @@
         <v>24</v>
       </c>
       <c r="C23">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D23">
         <v>375</v>
       </c>
       <c r="E23">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F23">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1617,16 +1610,16 @@
         <v>24</v>
       </c>
       <c r="C24">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D24">
         <v>375</v>
       </c>
       <c r="E24">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F24">
-        <v>4000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1637,16 +1630,16 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D25">
         <v>375</v>
       </c>
       <c r="E25">
-        <v>0.025</v>
+        <v>0.01</v>
       </c>
       <c r="F25">
-        <v>5000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1657,7 +1650,7 @@
         <v>33</v>
       </c>
       <c r="C26">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D26">
         <v>375</v>
@@ -1666,7 +1659,7 @@
         <v>0.025</v>
       </c>
       <c r="F26">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1677,7 +1670,7 @@
         <v>33</v>
       </c>
       <c r="C27">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D27">
         <v>375</v>
@@ -1686,7 +1679,7 @@
         <v>0.025</v>
       </c>
       <c r="F27">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1697,7 +1690,7 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D28">
         <v>375</v>
@@ -1706,7 +1699,7 @@
         <v>0.025</v>
       </c>
       <c r="F28">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1717,7 +1710,7 @@
         <v>33</v>
       </c>
       <c r="C29">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D29">
         <v>375</v>
@@ -1726,7 +1719,7 @@
         <v>0.025</v>
       </c>
       <c r="F29">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1737,7 +1730,7 @@
         <v>33</v>
       </c>
       <c r="C30">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D30">
         <v>375</v>
@@ -1746,7 +1739,7 @@
         <v>0.025</v>
       </c>
       <c r="F30">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1757,7 +1750,7 @@
         <v>39</v>
       </c>
       <c r="C31">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D31">
         <v>375</v>
@@ -1766,7 +1759,7 @@
         <v>0.025</v>
       </c>
       <c r="F31">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -1777,7 +1770,7 @@
         <v>39</v>
       </c>
       <c r="C32">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D32">
         <v>375</v>
@@ -1786,7 +1779,7 @@
         <v>0.025</v>
       </c>
       <c r="F32">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -1797,7 +1790,7 @@
         <v>39</v>
       </c>
       <c r="C33">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D33">
         <v>375</v>
@@ -1806,7 +1799,7 @@
         <v>0.025</v>
       </c>
       <c r="F33">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -1817,7 +1810,7 @@
         <v>39</v>
       </c>
       <c r="C34">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D34">
         <v>375</v>
@@ -1826,7 +1819,7 @@
         <v>0.025</v>
       </c>
       <c r="F34">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -1837,7 +1830,7 @@
         <v>39</v>
       </c>
       <c r="C35">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D35">
         <v>375</v>
@@ -1846,7 +1839,7 @@
         <v>0.025</v>
       </c>
       <c r="F35">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -1857,7 +1850,7 @@
         <v>39</v>
       </c>
       <c r="C36">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D36">
         <v>375</v>
@@ -1866,7 +1859,7 @@
         <v>0.025</v>
       </c>
       <c r="F36">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -1877,7 +1870,7 @@
         <v>39</v>
       </c>
       <c r="C37">
-        <v>115</v>
+        <v>375</v>
       </c>
       <c r="D37">
         <v>375</v>
@@ -1886,7 +1879,7 @@
         <v>0.025</v>
       </c>
       <c r="F37">
-        <v>4500</v>
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
@@ -1899,7 +1892,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
